--- a/C/chrVIII:0-46886_23_finemapping.xlsx
+++ b/C/chrVIII:0-46886_23_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4146" uniqueCount="4146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="4138">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -11780,19 +11780,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -12000,21 +11991,6 @@
   </si>
   <si>
     <t xml:space="preserve">QCR7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -12888,48 +12864,42 @@
         <v>3918</v>
       </c>
       <c r="Z1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA1" t="s">
         <v>3919</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>3920</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>3921</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>3922</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>3923</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>3924</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>3925</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>3926</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3927</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>3928</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>3930</v>
+        <v>3927</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -12983,59 +12953,57 @@
         <v>18914</v>
       </c>
       <c r="U2" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V2" t="n">
         <v>135790</v>
       </c>
       <c r="W2" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.240506012900001</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.037073434970216</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3931</v>
       </c>
       <c r="AD2" t="s">
         <v>19</v>
       </c>
       <c r="AE2" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>3935</v>
+        <v>3931</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>3932</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>3936</v>
+        <v>3933</v>
       </c>
       <c r="D3" t="s">
         <v>131</v>
@@ -13089,59 +13057,57 @@
         <v>18855</v>
       </c>
       <c r="U3" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V3" t="n">
         <v>75541</v>
       </c>
       <c r="W3" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.185402827650296</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0400339789631915</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>3931</v>
       </c>
       <c r="AD3" t="s">
         <v>19</v>
       </c>
       <c r="AE3" t="s">
+        <v>3931</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="s">
         <v>3934</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>3937</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>3938</v>
+        <v>3935</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -13195,62 +13161,60 @@
         <v>18914</v>
       </c>
       <c r="U4" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V4" t="n">
         <v>138698</v>
       </c>
       <c r="W4" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0.355426837497117</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0808009974860773</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3931</v>
       </c>
       <c r="AD4" t="s">
         <v>19</v>
       </c>
       <c r="AE4" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>3939</v>
+        <v>3931</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>3936</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>3940</v>
+        <v>3937</v>
       </c>
       <c r="D5" t="s">
-        <v>3941</v>
+        <v>3938</v>
       </c>
       <c r="E5" t="n">
         <v>18855</v>
@@ -13301,62 +13265,60 @@
         <v>27900</v>
       </c>
       <c r="U5" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V5" t="n">
         <v>126006</v>
       </c>
       <c r="W5" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.271257523895637</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0652984444882055</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3931</v>
       </c>
       <c r="AD5" t="s">
         <v>19</v>
       </c>
       <c r="AE5" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>3940</v>
+        <v>3931</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>3937</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>3942</v>
+        <v>3939</v>
       </c>
       <c r="D6" t="s">
-        <v>3941</v>
+        <v>3938</v>
       </c>
       <c r="E6" t="n">
         <v>27900</v>
@@ -13407,59 +13369,57 @@
         <v>27900</v>
       </c>
       <c r="U6" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V6" t="n">
         <v>406636</v>
       </c>
       <c r="W6" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.126745281075817</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.0307301091811296</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3931</v>
       </c>
       <c r="AD6" t="s">
         <v>19</v>
       </c>
       <c r="AE6" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>3943</v>
+        <v>3931</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>3940</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>3944</v>
+        <v>3941</v>
       </c>
       <c r="D7" t="s">
         <v>131</v>
@@ -13513,59 +13473,57 @@
         <v>18855</v>
       </c>
       <c r="U7" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V7" t="n">
         <v>366414</v>
       </c>
       <c r="W7" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.65532462392204</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.16910421410494</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3931</v>
       </c>
       <c r="AD7" t="s">
         <v>19</v>
       </c>
       <c r="AE7" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>3945</v>
+        <v>3931</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>3942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>3946</v>
+        <v>3943</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -13619,62 +13577,60 @@
         <v>18914</v>
       </c>
       <c r="U8" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V8" t="n">
         <v>188046</v>
       </c>
       <c r="W8" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.423865914287372</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.103698208021835</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3931</v>
       </c>
       <c r="AD8" t="s">
         <v>19</v>
       </c>
       <c r="AE8" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>3947</v>
+        <v>3931</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>3944</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>3948</v>
+        <v>3945</v>
       </c>
       <c r="D9" t="s">
-        <v>3949</v>
+        <v>3946</v>
       </c>
       <c r="E9" t="n">
         <v>18855</v>
@@ -13725,59 +13681,57 @@
         <v>35762</v>
       </c>
       <c r="U9" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V9" t="n">
         <v>377140</v>
       </c>
       <c r="W9" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.103973654466486</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0319121471342447</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3931</v>
       </c>
       <c r="AD9" t="s">
         <v>19</v>
       </c>
       <c r="AE9" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>3950</v>
+        <v>3931</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>3947</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>3951</v>
+        <v>3948</v>
       </c>
       <c r="D10" t="s">
         <v>131</v>
@@ -13831,62 +13785,60 @@
         <v>18855</v>
       </c>
       <c r="U10" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V10" t="n">
         <v>14933</v>
       </c>
       <c r="W10" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.743050465361932</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.228789588888629</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3931</v>
       </c>
       <c r="AD10" t="s">
         <v>19</v>
       </c>
       <c r="AE10" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>3951</v>
+        <v>3931</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>3948</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>3952</v>
+        <v>3949</v>
       </c>
       <c r="D11" t="s">
-        <v>3941</v>
+        <v>3938</v>
       </c>
       <c r="E11" t="n">
         <v>18855</v>
@@ -13937,59 +13889,57 @@
         <v>27900</v>
       </c>
       <c r="U11" t="s">
-        <v>3953</v>
+        <v>3950</v>
       </c>
       <c r="V11" t="n">
         <v>160</v>
       </c>
       <c r="W11" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.245183150226867</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0819751423121583</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3951</v>
       </c>
       <c r="AD11" t="s">
         <v>19</v>
       </c>
       <c r="AE11" t="s">
-        <v>3954</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3954</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>3952</v>
+        <v>3951</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>3949</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>3955</v>
+        <v>3952</v>
       </c>
       <c r="D12" t="s">
         <v>139</v>
@@ -14043,59 +13993,57 @@
         <v>14579</v>
       </c>
       <c r="U12" t="s">
-        <v>3953</v>
+        <v>3950</v>
       </c>
       <c r="V12" t="n">
         <v>591643</v>
       </c>
       <c r="W12" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.107637825392255</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0366616290476157</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3951</v>
       </c>
       <c r="AD12" t="s">
         <v>19</v>
       </c>
       <c r="AE12" t="s">
-        <v>3954</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3954</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>3956</v>
+        <v>3951</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>3953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>3957</v>
+        <v>3954</v>
       </c>
       <c r="D13" t="s">
         <v>131</v>
@@ -14149,62 +14097,60 @@
         <v>18855</v>
       </c>
       <c r="U13" t="s">
-        <v>3958</v>
+        <v>3955</v>
       </c>
       <c r="V13" t="n">
         <v>632355</v>
       </c>
       <c r="W13" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.121746285896926</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0469715739413295</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3956</v>
       </c>
       <c r="AD13" t="s">
         <v>19</v>
       </c>
       <c r="AE13" t="s">
-        <v>3959</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3959</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>3960</v>
+        <v>3956</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>3957</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>3961</v>
+        <v>3958</v>
       </c>
       <c r="D14" t="s">
-        <v>3962</v>
+        <v>3959</v>
       </c>
       <c r="E14" t="n">
         <v>8131</v>
@@ -14255,59 +14201,57 @@
         <v>34950</v>
       </c>
       <c r="U14" t="s">
-        <v>3963</v>
+        <v>3960</v>
       </c>
       <c r="V14" t="n">
         <v>396769</v>
       </c>
       <c r="W14" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.0884367539051585</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0342965615265483</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3961</v>
       </c>
       <c r="AD14" t="s">
         <v>19</v>
       </c>
       <c r="AE14" t="s">
-        <v>3964</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3964</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>3965</v>
+        <v>3961</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>3962</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>3966</v>
+        <v>3963</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -14361,59 +14305,57 @@
         <v>18914</v>
       </c>
       <c r="U15" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V15" t="n">
         <v>133043</v>
       </c>
       <c r="W15" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.346585339256453</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.138087452383661</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3931</v>
       </c>
       <c r="AD15" t="s">
         <v>19</v>
       </c>
       <c r="AE15" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>3967</v>
+        <v>3931</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>3964</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>3968</v>
+        <v>3965</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -14467,59 +14409,57 @@
         <v>18855</v>
       </c>
       <c r="U16" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V16" t="n">
         <v>375502</v>
       </c>
       <c r="W16" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.200047395355979</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0820756476996976</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3931</v>
       </c>
       <c r="AD16" t="s">
         <v>19</v>
       </c>
       <c r="AE16" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>3969</v>
+        <v>3931</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>3966</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>3970</v>
+        <v>3967</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -14573,62 +14513,60 @@
         <v>18914</v>
       </c>
       <c r="U17" t="s">
-        <v>3971</v>
+        <v>3968</v>
       </c>
       <c r="V17" t="n">
         <v>903661</v>
       </c>
       <c r="W17" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.16704977808835</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.470242773415009</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3969</v>
       </c>
       <c r="AD17" t="s">
         <v>19</v>
       </c>
       <c r="AE17" t="s">
-        <v>3972</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3972</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>3973</v>
+        <v>3969</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>3970</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>3974</v>
+        <v>3971</v>
       </c>
       <c r="D18" t="s">
-        <v>3975</v>
+        <v>3972</v>
       </c>
       <c r="E18" t="n">
         <v>8131</v>
@@ -14679,59 +14617,57 @@
         <v>33986</v>
       </c>
       <c r="U18" t="s">
-        <v>3976</v>
+        <v>3973</v>
       </c>
       <c r="V18" t="n">
         <v>254641</v>
       </c>
       <c r="W18" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.0776634292421543</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0297563787789214</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3974</v>
       </c>
       <c r="AD18" t="s">
         <v>19</v>
       </c>
       <c r="AE18" t="s">
-        <v>3977</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3977</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>3978</v>
+        <v>3974</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>3975</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>3979</v>
+        <v>3976</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -14785,27 +14721,31 @@
         <v>18914</v>
       </c>
       <c r="U19" t="s">
-        <v>3980</v>
+        <v>3977</v>
       </c>
       <c r="V19" t="n">
         <v>425157</v>
       </c>
       <c r="W19" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.0250080526624906</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.238261056568422</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>39</v>
       </c>
       <c r="AD19" t="s">
         <v>19</v>
@@ -14813,31 +14753,25 @@
       <c r="AE19" t="s">
         <v>39</v>
       </c>
-      <c r="AF19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="AF19" t="n">
         <v>4</v>
       </c>
-      <c r="AI19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>3981</v>
+      <c r="AG19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>3978</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>3982</v>
+        <v>3979</v>
       </c>
       <c r="D20" t="s">
         <v>131</v>
@@ -14891,59 +14825,57 @@
         <v>18855</v>
       </c>
       <c r="U20" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V20" t="n">
         <v>317501</v>
       </c>
       <c r="W20" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.397962948110695</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.175429681870884</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>3931</v>
       </c>
       <c r="AD20" t="s">
         <v>19</v>
       </c>
       <c r="AE20" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>3983</v>
+        <v>3931</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>3980</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>3984</v>
+        <v>3981</v>
       </c>
       <c r="D21" t="s">
         <v>131</v>
@@ -14997,59 +14929,57 @@
         <v>18855</v>
       </c>
       <c r="U21" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V21" t="n">
         <v>310210</v>
       </c>
       <c r="W21" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.458617515914975</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.184473928801052</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3931</v>
       </c>
       <c r="AD21" t="s">
         <v>19</v>
       </c>
       <c r="AE21" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>3985</v>
+        <v>3931</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>3982</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>3986</v>
+        <v>3983</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -15103,59 +15033,57 @@
         <v>18914</v>
       </c>
       <c r="U22" t="s">
-        <v>3931</v>
+        <v>3928</v>
       </c>
       <c r="V22" t="n">
         <v>22938</v>
       </c>
       <c r="W22" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.273973724541608</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.110797531664584</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>3931</v>
       </c>
       <c r="AD22" t="s">
         <v>19</v>
       </c>
       <c r="AE22" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>3934</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>3987</v>
+        <v>3931</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>3984</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>3988</v>
+        <v>3985</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -15209,59 +15137,57 @@
         <v>18914</v>
       </c>
       <c r="U23" t="s">
-        <v>3971</v>
+        <v>3968</v>
       </c>
       <c r="V23" t="n">
         <v>1354690</v>
       </c>
       <c r="W23" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z23" t="n">
         <v>-0.0767996121881186</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0314281548150089</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>3969</v>
       </c>
       <c r="AD23" t="s">
         <v>19</v>
       </c>
       <c r="AE23" t="s">
-        <v>3972</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>3972</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>3989</v>
+        <v>3969</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>3986</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3929</v>
+        <v>3926</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>3990</v>
+        <v>3987</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -15315,48 +15241,46 @@
         <v>18914</v>
       </c>
       <c r="U24" t="s">
-        <v>3971</v>
+        <v>3968</v>
       </c>
       <c r="V24" t="n">
         <v>1495927</v>
       </c>
       <c r="W24" t="s">
-        <v>3932</v>
+        <v>3929</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>3933</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>3930</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.105393356045289</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.0513885283915634</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>3969</v>
       </c>
       <c r="AD24" t="s">
         <v>19</v>
       </c>
       <c r="AE24" t="s">
-        <v>3972</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>3972</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>3991</v>
+        <v>3969</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>3988</v>
       </c>
     </row>
   </sheetData>
@@ -15435,37 +15359,28 @@
         <v>3915</v>
       </c>
       <c r="V1" t="s">
-        <v>3992</v>
+        <v>154</v>
       </c>
       <c r="W1" t="s">
-        <v>3993</v>
+        <v>3919</v>
       </c>
       <c r="X1" t="s">
-        <v>3994</v>
+        <v>3920</v>
       </c>
       <c r="Y1" t="s">
-        <v>3995</v>
+        <v>3921</v>
       </c>
       <c r="Z1" t="s">
-        <v>3996</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="AB1" t="s">
-        <v>3924</v>
+        <v>3989</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>3925</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3997</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>3928</v>
       </c>
     </row>
     <row r="2">
@@ -15473,10 +15388,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>3998</v>
+        <v>3990</v>
       </c>
       <c r="C2" t="s">
-        <v>3999</v>
+        <v>3991</v>
       </c>
       <c r="D2" t="n">
         <v>71979</v>
@@ -15533,37 +15448,28 @@
         <v>75412</v>
       </c>
       <c r="V2" t="n">
-        <v>15.8835410796952</v>
+        <v>0.521200383788887</v>
       </c>
       <c r="W2" t="n">
-        <v>9.52276874894183</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12.3809648745897</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.93488173686722</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12.0822419017827</v>
+        <v>0.0436810874018324</v>
+      </c>
+      <c r="X2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>19</v>
       </c>
       <c r="AA2" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" t="s">
-        <v>19</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>4000</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="3">
@@ -15571,7 +15477,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>4001</v>
+        <v>3993</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -15631,37 +15537,28 @@
         <v>18968</v>
       </c>
       <c r="V3" t="n">
-        <v>7.12333846980672</v>
+        <v>0.783053193122715</v>
       </c>
       <c r="W3" t="n">
-        <v>5.37658773854481</v>
-      </c>
-      <c r="X3" t="n">
-        <v>5.95083961438889</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.26656703162392</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.99205446106892</v>
+        <v>0.127763311377563</v>
+      </c>
+      <c r="X3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>19</v>
       </c>
       <c r="AA3" t="s">
         <v>19</v>
       </c>
-      <c r="AB3" t="s">
-        <v>19</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>4002</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="4">
@@ -15669,10 +15566,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>4003</v>
+        <v>3995</v>
       </c>
       <c r="C4" t="s">
-        <v>4004</v>
+        <v>3996</v>
       </c>
       <c r="D4" t="n">
         <v>8131</v>
@@ -15729,37 +15626,28 @@
         <v>8231</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.20806912525361</v>
+        <v>-0.995070091479009</v>
       </c>
       <c r="W4" t="n">
-        <v>-3.79910067737445</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-6.1363218160479</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-2.73070098388433</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-3.24045878507016</v>
+        <v>0.238233806128399</v>
+      </c>
+      <c r="X4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>19</v>
       </c>
       <c r="AA4" t="s">
         <v>19</v>
       </c>
-      <c r="AB4" t="s">
-        <v>19</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>4005</v>
+        <v>3997</v>
       </c>
     </row>
     <row r="5">
@@ -15770,7 +15658,7 @@
         <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>4004</v>
+        <v>3996</v>
       </c>
       <c r="D5" t="n">
         <v>8131</v>
@@ -15827,36 +15715,27 @@
         <v>6401</v>
       </c>
       <c r="V5" t="n">
-        <v>4.88906282939151</v>
+        <v>1.55938467097671</v>
       </c>
       <c r="W5" t="n">
-        <v>4.65983960282245</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.94672551729721</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0249842395350607</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.66308931846817</v>
+        <v>0.423773243897471</v>
+      </c>
+      <c r="X5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>19</v>
       </c>
       <c r="AA5" t="s">
         <v>19</v>
       </c>
-      <c r="AB5" t="s">
-        <v>19</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
         <v>137</v>
       </c>
     </row>
@@ -15865,10 +15744,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>4006</v>
+        <v>3998</v>
       </c>
       <c r="C6" t="s">
-        <v>3962</v>
+        <v>3959</v>
       </c>
       <c r="D6" t="n">
         <v>27900</v>
@@ -15925,37 +15804,28 @@
         <v>56649</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.01212480468498</v>
+        <v>-0.554807576256456</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.83259375705986</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.15654371017312</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-2.11430302034842</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-2.16496861977563</v>
+        <v>0.235463379190075</v>
+      </c>
+      <c r="X6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>19</v>
       </c>
       <c r="AA6" t="s">
         <v>19</v>
       </c>
-      <c r="AB6" t="s">
-        <v>19</v>
+      <c r="AB6" t="n">
+        <v>0.00078740157480315</v>
       </c>
       <c r="AC6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.00078740157480315</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>4007</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="7">
@@ -15963,10 +15833,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>4008</v>
+        <v>4000</v>
       </c>
       <c r="C7" t="s">
-        <v>4009</v>
+        <v>4001</v>
       </c>
       <c r="D7" t="n">
         <v>324302</v>
@@ -16023,37 +15893,28 @@
         <v>38695</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.45011188643021</v>
+        <v>-0.184262105891483</v>
       </c>
       <c r="W7" t="n">
-        <v>1.89620654813059</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-2.0168656218311</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-3.05053420245973</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.472849086951526</v>
+        <v>0.197047388742609</v>
+      </c>
+      <c r="X7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>19</v>
       </c>
       <c r="AA7" t="s">
         <v>19</v>
       </c>
-      <c r="AB7" t="s">
-        <v>19</v>
+      <c r="AB7" t="n">
+        <v>0.0020460358056266</v>
       </c>
       <c r="AC7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.0020460358056266</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>4010</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="8">
@@ -16061,10 +15922,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>4011</v>
+        <v>4003</v>
       </c>
       <c r="C8" t="s">
-        <v>4012</v>
+        <v>4004</v>
       </c>
       <c r="D8" t="n">
         <v>27900</v>
@@ -16121,37 +15982,28 @@
         <v>21783</v>
       </c>
       <c r="V8" t="n">
-        <v>0.80624761207604</v>
+        <v>0.127341231553415</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48240314801657</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.3641347333757</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-3.79157972146151</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.10997072663337</v>
+        <v>0.213162852203686</v>
+      </c>
+      <c r="X8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>19</v>
       </c>
       <c r="AA8" t="s">
         <v>19</v>
       </c>
-      <c r="AB8" t="s">
-        <v>19</v>
+      <c r="AB8" t="n">
+        <v>0.0037914691943128</v>
       </c>
       <c r="AC8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.0037914691943128</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>4013</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="9">
@@ -16159,10 +16011,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>4014</v>
+        <v>4006</v>
       </c>
       <c r="C9" t="s">
-        <v>4015</v>
+        <v>4007</v>
       </c>
       <c r="D9" t="n">
         <v>130538</v>
@@ -16219,37 +16071,28 @@
         <v>67652</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.00255717643228</v>
+        <v>-0.157144237014611</v>
       </c>
       <c r="W9" t="n">
-        <v>0.710709084574565</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.94210064096781</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-2.57605112594822</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.86439532382243</v>
+        <v>0.317083587215396</v>
+      </c>
+      <c r="X9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>19</v>
       </c>
       <c r="AA9" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" t="s">
-        <v>19</v>
+      <c r="AB9" t="n">
+        <v>0.0367493666675429</v>
       </c>
       <c r="AC9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.0367493666675429</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>4016</v>
+        <v>4008</v>
       </c>
     </row>
   </sheetData>
@@ -16280,34 +16123,34 @@
         <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>4017</v>
+        <v>4009</v>
       </c>
       <c r="G1" t="s">
         <v>2421</v>
       </c>
       <c r="H1" t="s">
-        <v>4018</v>
+        <v>4010</v>
       </c>
       <c r="I1" t="s">
-        <v>4019</v>
+        <v>4011</v>
       </c>
       <c r="J1" t="s">
         <v>2432</v>
       </c>
       <c r="K1" t="s">
-        <v>4020</v>
+        <v>4012</v>
       </c>
       <c r="L1" t="s">
-        <v>4021</v>
+        <v>4013</v>
       </c>
       <c r="M1" t="s">
-        <v>4022</v>
+        <v>4014</v>
       </c>
       <c r="N1" t="s">
-        <v>4023</v>
+        <v>4015</v>
       </c>
       <c r="O1" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="P1" t="s">
         <v>3915</v>
@@ -16327,30 +16170,30 @@
         <v>2867</v>
       </c>
       <c r="E2" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F2" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G2" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>4027</v>
+        <v>4019</v>
       </c>
       <c r="K2" t="s">
-        <v>4028</v>
+        <v>4020</v>
       </c>
       <c r="L2" t="s">
-        <v>4027</v>
+        <v>4019</v>
       </c>
       <c r="M2" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="N2" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O2"/>
       <c r="P2" t="n">
@@ -16371,30 +16214,30 @@
         <v>816</v>
       </c>
       <c r="E3" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F3" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G3" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>4031</v>
+        <v>4023</v>
       </c>
       <c r="K3" t="s">
-        <v>4032</v>
+        <v>4024</v>
       </c>
       <c r="L3" t="s">
-        <v>4031</v>
+        <v>4023</v>
       </c>
       <c r="M3" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="N3" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O3"/>
       <c r="P3" t="n">
@@ -16415,30 +16258,30 @@
         <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F4" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G4" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>4033</v>
+        <v>4025</v>
       </c>
       <c r="K4" t="s">
-        <v>4034</v>
+        <v>4026</v>
       </c>
       <c r="L4" t="s">
-        <v>4033</v>
+        <v>4025</v>
       </c>
       <c r="M4" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="N4" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
@@ -16459,13 +16302,13 @@
         <v>1146</v>
       </c>
       <c r="E5" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F5" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G5" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
@@ -16473,16 +16316,16 @@
         <v>136</v>
       </c>
       <c r="K5" t="s">
-        <v>4036</v>
+        <v>4028</v>
       </c>
       <c r="L5" t="s">
         <v>136</v>
       </c>
       <c r="M5" t="s">
-        <v>4037</v>
+        <v>4029</v>
       </c>
       <c r="N5" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O5" t="s">
         <v>137</v>
@@ -16505,33 +16348,33 @@
         <v>1863</v>
       </c>
       <c r="E6" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F6" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G6" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>4003</v>
+        <v>3995</v>
       </c>
       <c r="K6" t="s">
-        <v>4039</v>
+        <v>4031</v>
       </c>
       <c r="L6" t="s">
-        <v>4003</v>
+        <v>3995</v>
       </c>
       <c r="M6" t="s">
-        <v>4040</v>
+        <v>4032</v>
       </c>
       <c r="N6" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O6" t="s">
-        <v>4005</v>
+        <v>3997</v>
       </c>
       <c r="P6" t="n">
         <v>9282</v>
@@ -16551,33 +16394,33 @@
         <v>363</v>
       </c>
       <c r="E7" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F7" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G7" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>4041</v>
+        <v>4033</v>
       </c>
       <c r="K7" t="s">
-        <v>4042</v>
+        <v>4034</v>
       </c>
       <c r="L7" t="s">
-        <v>4041</v>
+        <v>4033</v>
       </c>
       <c r="M7" t="s">
-        <v>4043</v>
+        <v>4035</v>
       </c>
       <c r="N7" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O7" t="s">
-        <v>4044</v>
+        <v>4036</v>
       </c>
       <c r="P7" t="n">
         <v>12104</v>
@@ -16597,30 +16440,30 @@
         <v>708</v>
       </c>
       <c r="E8" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F8" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G8" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>4045</v>
+        <v>4037</v>
       </c>
       <c r="K8" t="s">
-        <v>4046</v>
+        <v>4038</v>
       </c>
       <c r="L8" t="s">
-        <v>4045</v>
+        <v>4037</v>
       </c>
       <c r="M8" t="s">
-        <v>4047</v>
+        <v>4039</v>
       </c>
       <c r="N8" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="n">
@@ -16641,13 +16484,13 @@
         <v>513</v>
       </c>
       <c r="E9" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F9" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G9" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
@@ -16655,16 +16498,16 @@
         <v>93</v>
       </c>
       <c r="K9" t="s">
-        <v>4048</v>
+        <v>4040</v>
       </c>
       <c r="L9" t="s">
         <v>93</v>
       </c>
       <c r="M9" t="s">
-        <v>4043</v>
+        <v>4035</v>
       </c>
       <c r="N9" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O9" t="s">
         <v>94</v>
@@ -16687,30 +16530,30 @@
         <v>453</v>
       </c>
       <c r="E10" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F10" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G10" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>4049</v>
+        <v>4041</v>
       </c>
       <c r="K10" t="s">
-        <v>4050</v>
+        <v>4042</v>
       </c>
       <c r="L10" t="s">
-        <v>4049</v>
+        <v>4041</v>
       </c>
       <c r="M10" t="s">
-        <v>4043</v>
+        <v>4035</v>
       </c>
       <c r="N10" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
@@ -16731,13 +16574,13 @@
         <v>450</v>
       </c>
       <c r="E11" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F11" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G11" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
@@ -16745,16 +16588,16 @@
         <v>111</v>
       </c>
       <c r="K11" t="s">
-        <v>4051</v>
+        <v>4043</v>
       </c>
       <c r="L11" t="s">
         <v>111</v>
       </c>
       <c r="M11" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="N11" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O11"/>
       <c r="P11" t="n">
@@ -16775,33 +16618,33 @@
         <v>1884</v>
       </c>
       <c r="E12" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F12" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G12" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>4001</v>
+        <v>3993</v>
       </c>
       <c r="K12" t="s">
-        <v>4052</v>
+        <v>4044</v>
       </c>
       <c r="L12" t="s">
-        <v>4001</v>
+        <v>3993</v>
       </c>
       <c r="M12" t="s">
-        <v>4053</v>
+        <v>4045</v>
       </c>
       <c r="N12" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O12" t="s">
-        <v>4002</v>
+        <v>3994</v>
       </c>
       <c r="P12" t="n">
         <v>20030</v>
@@ -16821,33 +16664,33 @@
         <v>1758</v>
       </c>
       <c r="E13" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F13" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G13" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>4011</v>
+        <v>4003</v>
       </c>
       <c r="K13" t="s">
-        <v>4054</v>
+        <v>4046</v>
       </c>
       <c r="L13" t="s">
-        <v>4011</v>
+        <v>4003</v>
       </c>
       <c r="M13" t="s">
-        <v>4055</v>
+        <v>4047</v>
       </c>
       <c r="N13" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O13" t="s">
-        <v>4013</v>
+        <v>4005</v>
       </c>
       <c r="P13" t="n">
         <v>22662</v>
@@ -16867,33 +16710,33 @@
         <v>1893</v>
       </c>
       <c r="E14" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F14" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G14" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>4056</v>
+        <v>4048</v>
       </c>
       <c r="K14" t="s">
-        <v>4057</v>
+        <v>4049</v>
       </c>
       <c r="L14" t="s">
-        <v>4056</v>
+        <v>4048</v>
       </c>
       <c r="M14" t="s">
-        <v>4058</v>
+        <v>4050</v>
       </c>
       <c r="N14" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O14" t="s">
-        <v>4059</v>
+        <v>4051</v>
       </c>
       <c r="P14" t="n">
         <v>24563</v>
@@ -16913,30 +16756,30 @@
         <v>402</v>
       </c>
       <c r="E15" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F15" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G15" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>4060</v>
+        <v>4052</v>
       </c>
       <c r="K15" t="s">
-        <v>4061</v>
+        <v>4053</v>
       </c>
       <c r="L15" t="s">
-        <v>4060</v>
+        <v>4052</v>
       </c>
       <c r="M15" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="N15" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O15"/>
       <c r="P15" t="n">
@@ -16957,33 +16800,33 @@
         <v>1641</v>
       </c>
       <c r="E16" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F16" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G16" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>4062</v>
+        <v>4054</v>
       </c>
       <c r="K16" t="s">
-        <v>4063</v>
+        <v>4055</v>
       </c>
       <c r="L16" t="s">
-        <v>4062</v>
+        <v>4054</v>
       </c>
       <c r="M16" t="s">
-        <v>4064</v>
+        <v>4056</v>
       </c>
       <c r="N16" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O16" t="s">
-        <v>4065</v>
+        <v>4057</v>
       </c>
       <c r="P16" t="n">
         <v>27061</v>
@@ -17003,33 +16846,33 @@
         <v>4779</v>
       </c>
       <c r="E17" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F17" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G17" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>4066</v>
+        <v>4058</v>
       </c>
       <c r="K17" t="s">
-        <v>4067</v>
+        <v>4059</v>
       </c>
       <c r="L17" t="s">
-        <v>4066</v>
+        <v>4058</v>
       </c>
       <c r="M17" t="s">
-        <v>4068</v>
+        <v>4060</v>
       </c>
       <c r="N17" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O17" t="s">
-        <v>4069</v>
+        <v>4061</v>
       </c>
       <c r="P17" t="n">
         <v>30367</v>
@@ -17049,33 +16892,33 @@
         <v>885</v>
       </c>
       <c r="E18" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F18" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G18" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>4070</v>
+        <v>4062</v>
       </c>
       <c r="K18" t="s">
-        <v>4071</v>
+        <v>4063</v>
       </c>
       <c r="L18" t="s">
-        <v>4070</v>
+        <v>4062</v>
       </c>
       <c r="M18" t="s">
-        <v>4072</v>
+        <v>4064</v>
       </c>
       <c r="N18" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O18" t="s">
-        <v>4073</v>
+        <v>4065</v>
       </c>
       <c r="P18" t="n">
         <v>33635</v>
@@ -17095,33 +16938,33 @@
         <v>771</v>
       </c>
       <c r="E19" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F19" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G19" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>4074</v>
+        <v>4066</v>
       </c>
       <c r="K19" t="s">
-        <v>4075</v>
+        <v>4067</v>
       </c>
       <c r="L19" t="s">
-        <v>4074</v>
+        <v>4066</v>
       </c>
       <c r="M19" t="s">
-        <v>4076</v>
+        <v>4068</v>
       </c>
       <c r="N19" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O19" t="s">
-        <v>4077</v>
+        <v>4069</v>
       </c>
       <c r="P19" t="n">
         <v>35640</v>
@@ -17141,33 +16984,33 @@
         <v>2130</v>
       </c>
       <c r="E20" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F20" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G20" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>4078</v>
+        <v>4070</v>
       </c>
       <c r="K20" t="s">
-        <v>4079</v>
+        <v>4071</v>
       </c>
       <c r="L20" t="s">
-        <v>4078</v>
+        <v>4070</v>
       </c>
       <c r="M20" t="s">
-        <v>4080</v>
+        <v>4072</v>
       </c>
       <c r="N20" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O20" t="s">
-        <v>4081</v>
+        <v>4073</v>
       </c>
       <c r="P20" t="n">
         <v>37444</v>
@@ -17187,33 +17030,33 @@
         <v>672</v>
       </c>
       <c r="E21" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F21" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G21" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>4008</v>
+        <v>4000</v>
       </c>
       <c r="K21" t="s">
-        <v>4082</v>
+        <v>4074</v>
       </c>
       <c r="L21" t="s">
-        <v>4008</v>
+        <v>4000</v>
       </c>
       <c r="M21" t="s">
-        <v>4083</v>
+        <v>4075</v>
       </c>
       <c r="N21" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O21" t="s">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="P21" t="n">
         <v>39150</v>
@@ -17233,33 +17076,33 @@
         <v>5607</v>
       </c>
       <c r="E22" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F22" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G22" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>4084</v>
+        <v>4076</v>
       </c>
       <c r="K22" t="s">
-        <v>4085</v>
+        <v>4077</v>
       </c>
       <c r="L22" t="s">
-        <v>4084</v>
+        <v>4076</v>
       </c>
       <c r="M22" t="s">
-        <v>4086</v>
+        <v>4078</v>
       </c>
       <c r="N22" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O22" t="s">
-        <v>4087</v>
+        <v>4079</v>
       </c>
       <c r="P22" t="n">
         <v>42887</v>
@@ -17279,33 +17122,33 @@
         <v>2040</v>
       </c>
       <c r="E23" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F23" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G23" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>4088</v>
+        <v>4080</v>
       </c>
       <c r="K23" t="s">
-        <v>4089</v>
+        <v>4081</v>
       </c>
       <c r="L23" t="s">
-        <v>4088</v>
+        <v>4080</v>
       </c>
       <c r="M23" t="s">
-        <v>4090</v>
+        <v>4082</v>
       </c>
       <c r="N23" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O23" t="s">
-        <v>4091</v>
+        <v>4083</v>
       </c>
       <c r="P23" t="n">
         <v>46948</v>
@@ -17325,33 +17168,33 @@
         <v>1818</v>
       </c>
       <c r="E24" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F24" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G24" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>4092</v>
+        <v>4084</v>
       </c>
       <c r="K24" t="s">
-        <v>4093</v>
+        <v>4085</v>
       </c>
       <c r="L24" t="s">
-        <v>4092</v>
+        <v>4084</v>
       </c>
       <c r="M24" t="s">
-        <v>4094</v>
+        <v>4086</v>
       </c>
       <c r="N24" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O24" t="s">
-        <v>4095</v>
+        <v>4087</v>
       </c>
       <c r="P24" t="n">
         <v>49672</v>
@@ -17371,33 +17214,33 @@
         <v>1878</v>
       </c>
       <c r="E25" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F25" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G25" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>4096</v>
+        <v>4088</v>
       </c>
       <c r="K25" t="s">
-        <v>4097</v>
+        <v>4089</v>
       </c>
       <c r="L25" t="s">
-        <v>4096</v>
+        <v>4088</v>
       </c>
       <c r="M25" t="s">
-        <v>4098</v>
+        <v>4090</v>
       </c>
       <c r="N25" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O25" t="s">
-        <v>4099</v>
+        <v>4091</v>
       </c>
       <c r="P25" t="n">
         <v>52050</v>
@@ -17417,30 +17260,30 @@
         <v>948</v>
       </c>
       <c r="E26" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F26" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G26" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>4100</v>
+        <v>4092</v>
       </c>
       <c r="K26" t="s">
-        <v>4101</v>
+        <v>4093</v>
       </c>
       <c r="L26" t="s">
-        <v>4100</v>
+        <v>4092</v>
       </c>
       <c r="M26" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="N26" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O26"/>
       <c r="P26" t="n">
@@ -17461,33 +17304,33 @@
         <v>999</v>
       </c>
       <c r="E27" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F27" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G27" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>4102</v>
+        <v>4094</v>
       </c>
       <c r="K27" t="s">
-        <v>4103</v>
+        <v>4095</v>
       </c>
       <c r="L27" t="s">
-        <v>4102</v>
+        <v>4094</v>
       </c>
       <c r="M27" t="s">
-        <v>4104</v>
+        <v>4096</v>
       </c>
       <c r="N27" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O27" t="s">
-        <v>4105</v>
+        <v>4097</v>
       </c>
       <c r="P27" t="n">
         <v>55350</v>
@@ -17507,33 +17350,33 @@
         <v>2142</v>
       </c>
       <c r="E28" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F28" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G28" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>4006</v>
+        <v>3998</v>
       </c>
       <c r="K28" t="s">
-        <v>4106</v>
+        <v>4098</v>
       </c>
       <c r="L28" t="s">
-        <v>4006</v>
+        <v>3998</v>
       </c>
       <c r="M28" t="s">
-        <v>4107</v>
+        <v>4099</v>
       </c>
       <c r="N28" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O28" t="s">
-        <v>4007</v>
+        <v>3999</v>
       </c>
       <c r="P28" t="n">
         <v>57720</v>
@@ -17553,33 +17396,33 @@
         <v>3441</v>
       </c>
       <c r="E29" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F29" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G29" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="K29" t="s">
-        <v>4109</v>
+        <v>4101</v>
       </c>
       <c r="L29" t="s">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="M29" t="s">
-        <v>4110</v>
+        <v>4102</v>
       </c>
       <c r="N29" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O29" t="s">
-        <v>4111</v>
+        <v>4103</v>
       </c>
       <c r="P29" t="n">
         <v>60843</v>
@@ -17599,33 +17442,33 @@
         <v>1197</v>
       </c>
       <c r="E30" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F30" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G30" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>4112</v>
+        <v>4104</v>
       </c>
       <c r="K30" t="s">
-        <v>4113</v>
+        <v>4105</v>
       </c>
       <c r="L30" t="s">
-        <v>4112</v>
+        <v>4104</v>
       </c>
       <c r="M30" t="s">
-        <v>4114</v>
+        <v>4106</v>
       </c>
       <c r="N30" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O30" t="s">
-        <v>4115</v>
+        <v>4107</v>
       </c>
       <c r="P30" t="n">
         <v>63559</v>
@@ -17645,33 +17488,33 @@
         <v>1398</v>
       </c>
       <c r="E31" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F31" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G31" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>4116</v>
+        <v>4108</v>
       </c>
       <c r="K31" t="s">
-        <v>4117</v>
+        <v>4109</v>
       </c>
       <c r="L31" t="s">
-        <v>4116</v>
+        <v>4108</v>
       </c>
       <c r="M31" t="s">
-        <v>4043</v>
+        <v>4035</v>
       </c>
       <c r="N31" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O31" t="s">
-        <v>4118</v>
+        <v>4110</v>
       </c>
       <c r="P31" t="n">
         <v>65160</v>
@@ -17691,33 +17534,33 @@
         <v>1215</v>
       </c>
       <c r="E32" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F32" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G32" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>4119</v>
+        <v>4111</v>
       </c>
       <c r="K32" t="s">
-        <v>4120</v>
+        <v>4112</v>
       </c>
       <c r="L32" t="s">
-        <v>4119</v>
+        <v>4111</v>
       </c>
       <c r="M32" t="s">
-        <v>4121</v>
+        <v>4113</v>
       </c>
       <c r="N32" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O32" t="s">
-        <v>4122</v>
+        <v>4114</v>
       </c>
       <c r="P32" t="n">
         <v>66849</v>
@@ -17737,33 +17580,33 @@
         <v>1818</v>
       </c>
       <c r="E33" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F33" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G33" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>4014</v>
+        <v>4006</v>
       </c>
       <c r="K33" t="s">
-        <v>4123</v>
+        <v>4115</v>
       </c>
       <c r="L33" t="s">
-        <v>4014</v>
+        <v>4006</v>
       </c>
       <c r="M33" t="s">
-        <v>4043</v>
+        <v>4035</v>
       </c>
       <c r="N33" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O33" t="s">
-        <v>4016</v>
+        <v>4008</v>
       </c>
       <c r="P33" t="n">
         <v>68640</v>
@@ -17783,30 +17626,30 @@
         <v>363</v>
       </c>
       <c r="E34" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F34" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G34" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>4124</v>
+        <v>4116</v>
       </c>
       <c r="K34" t="s">
-        <v>4125</v>
+        <v>4117</v>
       </c>
       <c r="L34" t="s">
-        <v>4124</v>
+        <v>4116</v>
       </c>
       <c r="M34" t="s">
-        <v>4126</v>
+        <v>4118</v>
       </c>
       <c r="N34" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O34"/>
       <c r="P34" t="n">
@@ -17827,30 +17670,30 @@
         <v>1599</v>
       </c>
       <c r="E35" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F35" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G35" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>4127</v>
+        <v>4119</v>
       </c>
       <c r="K35" t="s">
-        <v>4128</v>
+        <v>4120</v>
       </c>
       <c r="L35" t="s">
-        <v>4127</v>
+        <v>4119</v>
       </c>
       <c r="M35" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="N35" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O35"/>
       <c r="P35" t="n">
@@ -17871,33 +17714,33 @@
         <v>2208</v>
       </c>
       <c r="E36" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F36" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G36" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>4129</v>
+        <v>4121</v>
       </c>
       <c r="K36" t="s">
-        <v>4130</v>
+        <v>4122</v>
       </c>
       <c r="L36" t="s">
-        <v>4129</v>
+        <v>4121</v>
       </c>
       <c r="M36" t="s">
-        <v>4131</v>
+        <v>4123</v>
       </c>
       <c r="N36" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O36" t="s">
-        <v>4132</v>
+        <v>4124</v>
       </c>
       <c r="P36" t="n">
         <v>73140</v>
@@ -17917,30 +17760,30 @@
         <v>84</v>
       </c>
       <c r="E37" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F37" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G37" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>4133</v>
+        <v>4125</v>
       </c>
       <c r="K37" t="s">
-        <v>4134</v>
+        <v>4126</v>
       </c>
       <c r="L37" t="s">
-        <v>4133</v>
+        <v>4125</v>
       </c>
       <c r="M37" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="N37" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O37"/>
       <c r="P37" t="n">
@@ -17961,33 +17804,33 @@
         <v>366</v>
       </c>
       <c r="E38" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F38" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G38" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>3998</v>
+        <v>3990</v>
       </c>
       <c r="K38" t="s">
-        <v>4135</v>
+        <v>4127</v>
       </c>
       <c r="L38" t="s">
-        <v>3998</v>
+        <v>3990</v>
       </c>
       <c r="M38" t="s">
-        <v>4136</v>
+        <v>4128</v>
       </c>
       <c r="N38" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O38" t="s">
-        <v>4000</v>
+        <v>3992</v>
       </c>
       <c r="P38" t="n">
         <v>75594</v>
@@ -18007,33 +17850,33 @@
         <v>1218</v>
       </c>
       <c r="E39" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F39" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G39" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" t="s">
-        <v>4137</v>
+        <v>4129</v>
       </c>
       <c r="K39" t="s">
-        <v>4138</v>
+        <v>4130</v>
       </c>
       <c r="L39" t="s">
-        <v>4137</v>
+        <v>4129</v>
       </c>
       <c r="M39" t="s">
-        <v>4043</v>
+        <v>4035</v>
       </c>
       <c r="N39" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O39" t="s">
-        <v>4139</v>
+        <v>4131</v>
       </c>
       <c r="P39" t="n">
         <v>76706</v>
@@ -18053,33 +17896,33 @@
         <v>924</v>
       </c>
       <c r="E40" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="F40" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G40" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" t="s">
-        <v>4140</v>
+        <v>4132</v>
       </c>
       <c r="K40" t="s">
-        <v>4141</v>
+        <v>4133</v>
       </c>
       <c r="L40" t="s">
-        <v>4140</v>
+        <v>4132</v>
       </c>
       <c r="M40" t="s">
-        <v>4043</v>
+        <v>4035</v>
       </c>
       <c r="N40" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
       <c r="O40" t="s">
-        <v>4142</v>
+        <v>4134</v>
       </c>
       <c r="P40" t="n">
         <v>77892</v>
@@ -18099,30 +17942,30 @@
         <v>1482</v>
       </c>
       <c r="E41" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="F41" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
       <c r="G41" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" t="s">
-        <v>4143</v>
+        <v>4135</v>
       </c>
       <c r="K41" t="s">
-        <v>4144</v>
+        <v>4136</v>
       </c>
       <c r="L41" t="s">
-        <v>4143</v>
+        <v>4135</v>
       </c>
       <c r="M41" t="s">
-        <v>4145</v>
+        <v>4137</v>
       </c>
       <c r="N41" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
       <c r="O41"/>
       <c r="P41" t="n">
